--- a/2_calculated_metrics/gbls_corpus_metrics/gbls_feature_overview.xlsx
+++ b/2_calculated_metrics/gbls_corpus_metrics/gbls_feature_overview.xlsx
@@ -1,42 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year Counts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Feature Counts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Type" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Review" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Type" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary Methodology" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library Context" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Format" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service Area" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audience" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intended Outcome" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Confidence" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Year Counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All Feature Counts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Data Dictionary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Source_Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Peer_Review" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Evidence_Type" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Primary_Methodology" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Library_Context" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Game_Format" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Service_Area" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Audience" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Intended_Outcome" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Coding_Confidence" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dashboard'!$A$1:$B$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Year Counts'!$A$1:$C$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Feature Counts'!$A$1:$F$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Dictionary'!$A$1:$D$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Source Type'!$A$1:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Peer Review'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Evidence Type'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Primary Methodology'!$A$1:$F$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Library Context'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Game Format'!$A$1:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Service Area'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Audience'!$A$1:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Intended Outcome'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Coding Confidence'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Dictionary'!$A$1:$C$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Source_Type'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Peer_Review'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Evidence_Type'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Primary_Methodology'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Library_Context'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Game_Format'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Service_Area'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Audience'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Intended_Outcome'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Coding_Confidence'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +44,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,17 +54,26 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -73,20 +81,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,117 +456,273 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Total Articles</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>200</v>
-      </c>
-    </row>
+          <t>GBLS Corpus Metrics – Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Earliest Year</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1950</v>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latest Year</t>
+          <t>Total Articles</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2025</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unique Feature Labels</t>
+          <t>Earliest Year</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>87</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total Article Feature Assignments</t>
+          <t>Latest Year</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2277</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mean Features Per Article</t>
+          <t>Unique Feature Labels</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.385</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Median Summary Word Count</t>
+          <t>Total Article Feature Assignments</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>651.5</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Articles With Contributions</t>
+          <t>Mean Features Per Article</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>11.385</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Median Summary Word Count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>621.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Articles With Contributions</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Not Dated Articles</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Feature Group</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Unique Values</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Total Assignments</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Source_Type</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Peer_Review</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Evidence_Type</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Primary_Methodology</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Library_Context</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Game_Format</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Service_Area</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Intended_Outcome</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Coding_Confidence</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -574,44 +733,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -620,269 +773,214 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>digital_game</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>62</v>
+      </c>
       <c r="C2" t="n">
-        <v>62</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>multiple_game_formats</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>tabletop_game</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>tabletop_roleplaying_game</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>19</v>
+      </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>9.5</v>
       </c>
       <c r="E5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>virtual_or_augmented_reality</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>14</v>
+      </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>gamification</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>13</v>
+      </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>6.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>escape_room_or_breakout_box</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>unspecified_game_format</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>3.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F9" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>game_creation</t>
-        </is>
+          <t>toy_or_open_play</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F10" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>toy_or_open_play</t>
-        </is>
+          <t>game_creation</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>game_format</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>pervasive_game</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F12" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -893,44 +991,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -939,245 +1031,195 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>learning_and_literacy</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>99</v>
+      </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>49.5</v>
       </c>
       <c r="E2" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>collections_and_access</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>77</v>
+      </c>
       <c r="C3" t="n">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>38.5</v>
       </c>
       <c r="E3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>programming_and_facilitation</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>56</v>
+      </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>discovery_and_advisory</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>35</v>
+      </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>17.5</v>
       </c>
       <c r="E5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>community_and_inclusion</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>29</v>
+      </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>14.5</v>
       </c>
       <c r="E6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>professional_capacity</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>19</v>
+      </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>9.5</v>
       </c>
       <c r="E7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>cultural_heritage_and_research</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" t="n">
-        <v>7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>space_and_infrastructure</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>6.5</v>
       </c>
       <c r="E9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F9" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>outreach_and_partnerships</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>2.5</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F10" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>service_area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>creation_and_making</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1188,44 +1230,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -1234,269 +1270,214 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>not_applicable</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>123</v>
+      </c>
       <c r="C2" t="n">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>61.5</v>
       </c>
       <c r="E2" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>students</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>51</v>
+      </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>25.5</v>
       </c>
       <c r="E3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>teens</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>18</v>
+      </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>children</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>13</v>
+      </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>6.5</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>general_public</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>families</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>3.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>underserved_or_special_population</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>young_adults</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>educators</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F10" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>adults</t>
-        </is>
+          <t>older_adults</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>audience</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>older_adults</t>
-        </is>
+          <t>adults</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F12" t="n">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1507,44 +1488,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -1553,245 +1528,195 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>not_applicable</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>90</v>
+      </c>
       <c r="C2" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>learning_and_literacy</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>64</v>
+      </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>discovery_and_advisory</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>25</v>
+      </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>belonging_and_community</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>creativity_and_production</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>17</v>
+      </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>8.5</v>
       </c>
       <c r="E6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>equitable_access</t>
-        </is>
+          <t>institutional_capacity</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>institutional_capacity</t>
-        </is>
+          <t>equitable_access</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>engagement_and_participation</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>5.5</v>
       </c>
       <c r="E9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F9" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>cultural_stewardship_and_preservation</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>wellness_and_resilience</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F11" t="n">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1802,44 +1727,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -1848,77 +1767,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>high</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>195</v>
+      </c>
       <c r="C2" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>97.5</v>
       </c>
       <c r="E2" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>low</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1938,17 +1842,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>year_label</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
@@ -2264,32 +2168,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -2298,22 +2202,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>peer_reviewed_journal_article</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D2" t="n">
         <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>61.5</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -2322,22 +2226,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>toolkit_or_guidance_document</t>
+          <t>students</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D3" t="n">
         <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -2346,22 +2250,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>professional_publication</t>
+          <t>teens</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
         <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -2370,22 +2274,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>conference_paper</t>
+          <t>children</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>200</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -2394,22 +2298,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>book_chapter</t>
+          <t>general_public</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>200</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -2418,70 +2322,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dataset_or_archive</t>
+          <t>families</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>blog_or_web_article</t>
+          <t>underserved_or_special_population</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>young_adults</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>200</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
@@ -2490,60 +2394,60 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dissertation_or_thesis</t>
+          <t>educators</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>200</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>government_or_foundation_report</t>
+          <t>older_adults</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>audience</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>unpublished_document</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2556,28 +2460,28 @@
         <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>coding_confidence</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>peer_reviewed</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>195</v>
       </c>
       <c r="D13" t="n">
         <v>200</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>97.5</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -2586,22 +2490,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>coding_confidence</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>editorial_reviewed</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>200</v>
       </c>
       <c r="E14" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -2610,22 +2514,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>coding_confidence</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>200</v>
       </c>
       <c r="E15" t="n">
-        <v>17.5</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -2634,25 +2538,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>empirical_study</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D16" t="n">
         <v>200</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>39.5</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2663,20 +2567,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>empirical_study</t>
+          <t>practitioner_reflection</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D17" t="n">
         <v>200</v>
       </c>
       <c r="E17" t="n">
-        <v>39.5</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -2687,20 +2591,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>practitioner_reflection</t>
+          <t>theoretical_or_conceptual</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>200</v>
       </c>
       <c r="E18" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2711,20 +2615,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>theoretical_or_conceptual</t>
+          <t>implementation_case</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
         <v>200</v>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2735,20 +2639,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>implementation_case</t>
+          <t>evidence_synthesis</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
         <v>200</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -2759,7 +2663,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>evidence_synthesis</t>
+          <t>instrument_or_framework_development</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2783,511 +2687,511 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>instrument_or_framework_development</t>
+          <t>content_or_artifact_analysis</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
         <v>200</v>
       </c>
       <c r="E22" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>content_or_artifact_analysis</t>
+          <t>digital_game</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="D23" t="n">
         <v>200</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>multiple_game_formats</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" t="n">
         <v>200</v>
       </c>
       <c r="E24" t="n">
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>theoretical_or_conceptual</t>
+          <t>tabletop_game</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>200</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>case_or_design_study</t>
+          <t>tabletop_roleplaying_game</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
         <v>200</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mixed_methods</t>
+          <t>virtual_or_augmented_reality</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
         <v>200</v>
       </c>
       <c r="E27" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qualitative_study</t>
+          <t>gamification</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
         <v>200</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>experimental_study</t>
+          <t>escape_room_or_breakout_box</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>200</v>
       </c>
       <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
         <v>7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>unspecified_game_format</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
         <v>200</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>evidence_synthesis</t>
+          <t>toy_or_open_play</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>200</v>
       </c>
       <c r="E31" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>content_analysis</t>
+          <t>game_creation</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>200</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>historical_analysis</t>
+          <t>pervasive_game</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>200</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>participatory_design</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="D34" t="n">
         <v>200</v>
       </c>
       <c r="E34" t="n">
+        <v>45</v>
+      </c>
+      <c r="F34" t="n">
         <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>action_research</t>
+          <t>learning_and_literacy</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D35" t="n">
         <v>200</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5</v>
+        <v>32</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>non_library_context</t>
+          <t>discovery_and_advisory</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D36" t="n">
         <v>200</v>
       </c>
       <c r="E36" t="n">
-        <v>23.5</v>
+        <v>12.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>unspecified_library_context</t>
+          <t>belonging_and_community</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D37" t="n">
         <v>200</v>
       </c>
       <c r="E37" t="n">
-        <v>23.5</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>public_library</t>
+          <t>creativity_and_production</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D38" t="n">
         <v>200</v>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>8.5</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>academic_library</t>
+          <t>institutional_capacity</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D39" t="n">
         <v>200</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>cultural_heritage_institution</t>
+          <t>equitable_access</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D40" t="n">
         <v>200</v>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>multiple_library_types</t>
+          <t>engagement_and_participation</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
         <v>200</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>school_library</t>
+          <t>cultural_stewardship_and_preservation</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
         <v>200</v>
       </c>
       <c r="E42" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>library_school</t>
+          <t>wellness_and_resilience</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3300,28 +3204,28 @@
         <v>1.5</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>digital_game</t>
+          <t>non_library_context</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D44" t="n">
         <v>200</v>
       </c>
       <c r="E44" t="n">
-        <v>31</v>
+        <v>23.5</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -3330,396 +3234,396 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>multiple_game_formats</t>
+          <t>unspecified_library_context</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D45" t="n">
         <v>200</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>tabletop_game</t>
+          <t>public_library</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D46" t="n">
         <v>200</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>tabletop_roleplaying_game</t>
+          <t>cultural_heritage_institution</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D47" t="n">
         <v>200</v>
       </c>
       <c r="E47" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>virtual_or_augmented_reality</t>
+          <t>academic_library</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D48" t="n">
         <v>200</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gamification</t>
+          <t>multiple_library_types</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
         <v>200</v>
       </c>
       <c r="E49" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>escape_room_or_breakout_box</t>
+          <t>school_library</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
         <v>200</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>unspecified_game_format</t>
+          <t>library_school</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
         <v>200</v>
       </c>
       <c r="E51" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>peer_review</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>game_creation</t>
+          <t>peer_reviewed</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>116</v>
       </c>
       <c r="D52" t="n">
         <v>200</v>
       </c>
       <c r="E52" t="n">
-        <v>1.5</v>
+        <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>peer_review</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>toy_or_open_play</t>
+          <t>editorial_reviewed</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D53" t="n">
         <v>200</v>
       </c>
       <c r="E53" t="n">
-        <v>1.5</v>
+        <v>19.5</v>
       </c>
       <c r="F53" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>game_format</t>
+          <t>peer_review</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pervasive_game</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D54" t="n">
         <v>200</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5</v>
+        <v>17.5</v>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>peer_review</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>learning_and_literacy</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
         <v>200</v>
       </c>
       <c r="E55" t="n">
-        <v>49.5</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>collections_and_access</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D56" t="n">
         <v>200</v>
       </c>
       <c r="E56" t="n">
-        <v>38.5</v>
+        <v>25.5</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>programming_and_facilitation</t>
+          <t>theoretical_or_conceptual</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D57" t="n">
         <v>200</v>
       </c>
       <c r="E57" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>discovery_and_advisory</t>
+          <t>case_or_design_study</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D58" t="n">
         <v>200</v>
       </c>
       <c r="E58" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>community_and_inclusion</t>
+          <t>mixed_methods</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D59" t="n">
         <v>200</v>
       </c>
       <c r="E59" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>professional_capacity</t>
+          <t>qualitative_study</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D60" t="n">
         <v>200</v>
       </c>
       <c r="E60" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>cultural_heritage_and_research</t>
+          <t>experimental_study</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3732,655 +3636,655 @@
         <v>7</v>
       </c>
       <c r="F61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>space_and_infrastructure</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D62" t="n">
         <v>200</v>
       </c>
       <c r="E62" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>outreach_and_partnerships</t>
+          <t>evidence_synthesis</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D63" t="n">
         <v>200</v>
       </c>
       <c r="E63" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>creation_and_making</t>
+          <t>content_analysis</t>
         </is>
       </c>
       <c r="C64" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>200</v>
+      </c>
+      <c r="E64" t="n">
         <v>4</v>
       </c>
-      <c r="D64" t="n">
-        <v>200</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2</v>
-      </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>historical_analysis</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
         <v>200</v>
       </c>
       <c r="E65" t="n">
-        <v>61.5</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>participatory_design</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>200</v>
       </c>
       <c r="E66" t="n">
-        <v>25.5</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>teens</t>
+          <t>action_research</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>200</v>
       </c>
       <c r="E67" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>children</t>
+          <t>learning_and_literacy</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D68" t="n">
         <v>200</v>
       </c>
       <c r="E68" t="n">
-        <v>6.5</v>
+        <v>49.5</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>general_public</t>
+          <t>collections_and_access</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="D69" t="n">
         <v>200</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>38.5</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>families</t>
+          <t>programming_and_facilitation</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D70" t="n">
         <v>200</v>
       </c>
       <c r="E70" t="n">
-        <v>3.5</v>
+        <v>28</v>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>underserved_or_special_population</t>
+          <t>discovery_and_advisory</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D71" t="n">
         <v>200</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>17.5</v>
       </c>
       <c r="F71" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>young_adults</t>
+          <t>community_and_inclusion</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D72" t="n">
         <v>200</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>14.5</v>
       </c>
       <c r="F72" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>educators</t>
+          <t>professional_capacity</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D73" t="n">
         <v>200</v>
       </c>
       <c r="E73" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>adults</t>
+          <t>cultural_heritage_and_research</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D74" t="n">
         <v>200</v>
       </c>
       <c r="E74" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>older_adults</t>
+          <t>space_and_infrastructure</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
         <v>200</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="F75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>outreach_and_partnerships</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
         <v>200</v>
       </c>
       <c r="E76" t="n">
-        <v>45</v>
+        <v>2.5</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>service_area</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>learning_and_literacy</t>
+          <t>creation_and_making</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>200</v>
       </c>
       <c r="E77" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>discovery_and_advisory</t>
+          <t>peer_reviewed_journal_article</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="D78" t="n">
         <v>200</v>
       </c>
       <c r="E78" t="n">
-        <v>12.5</v>
+        <v>58</v>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>belonging_and_community</t>
+          <t>toolkit_or_guidance_document</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D79" t="n">
         <v>200</v>
       </c>
       <c r="E79" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>creativity_and_production</t>
+          <t>professional_publication</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D80" t="n">
         <v>200</v>
       </c>
       <c r="E80" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>equitable_access</t>
+          <t>conference_paper</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
         <v>200</v>
       </c>
       <c r="E81" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>institutional_capacity</t>
+          <t>dataset_or_archive</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
         <v>200</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>engagement_and_participation</t>
+          <t>book_chapter</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
         <v>200</v>
       </c>
       <c r="E83" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cultural_stewardship_and_preservation</t>
+          <t>blog_or_web_article</t>
         </is>
       </c>
       <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="n">
+        <v>200</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F84" t="n">
         <v>6</v>
-      </c>
-      <c r="D84" t="n">
-        <v>200</v>
-      </c>
-      <c r="E84" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>wellness_and_resilience</t>
+          <t>dissertation_or_thesis</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
         <v>200</v>
       </c>
       <c r="E85" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>government_or_foundation_report</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>195</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
         <v>200</v>
       </c>
       <c r="E86" t="n">
-        <v>97.5</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>200</v>
       </c>
       <c r="E87" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>unpublished_document</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
         <v>200</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4395,32 +4299,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>grain</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>primary_key</t>
         </is>
@@ -4434,15 +4332,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Full article table with summary text</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>Full parsed article data including summary text</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
         <is>
           <t>article_id</t>
         </is>
@@ -4456,15 +4349,10 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Article table without summary text</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>Article data without summary text</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
         <is>
           <t>article_id</t>
         </is>
@@ -4478,17 +4366,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>one row per article-feature assignment</t>
+          <t>One row per article-feature assignment (present=1)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Long-form controlled metadata</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>article_id + feature_group + feature_value</t>
+          <t>article_id + feature_column</t>
         </is>
       </c>
     </row>
@@ -4500,15 +4383,10 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Binary article × feature matrix across all feature groups</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>Binary matrix of every coded feature</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
         <is>
           <t>article_id</t>
         </is>
@@ -4522,15 +4400,10 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>one row per proposed contribution</t>
+          <t>One row per extracted proposed contribution</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>Suggested review contributions</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
         <is>
           <t>article_id + contribution_number</t>
         </is>
@@ -4544,15 +4417,10 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Aggregate counts per feature_group + feature_value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>Corpus prevalence by feature</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
         <is>
           <t>feature_group + feature_value</t>
         </is>
@@ -4566,15 +4434,10 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>one row per year</t>
+          <t>Article counts by publication year</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>Publication volume</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
         <is>
           <t>year_label</t>
         </is>
@@ -4588,15 +4451,10 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>one row per year-feature combination</t>
+          <t>Feature counts broken down by publication year</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>Feature prevalence over time</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>year + feature_group + feature_value</t>
         </is>
@@ -4610,15 +4468,10 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>one row per feature pair</t>
+          <t>Unordered pairs of features co-occurring in ≥2 articles</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>Feature co-occurrence in at least two articles</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>feature pair</t>
         </is>
@@ -4632,15 +4485,10 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>one row per metric</t>
+          <t>Headline corpus metrics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Headline corpus metrics</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
@@ -4649,445 +4497,447 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>source_type_counts.csv</t>
+          <t>dataset_summary.json</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Same as dataset_summary.csv in JSON</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Counts for Source Type</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source_type_matrix.csv</t>
+          <t>data_dictionary.csv</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>This file – documents all generated artifacts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Binary matrix for Source Type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>file</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>peer_review_counts.csv</t>
+          <t>feature_datasets_readme.md</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Human-readable guide to the metric files</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Counts for Peer Review</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>peer_review_matrix.csv</t>
+          <t>validation_report.json</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Parse and consistency validation results</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Binary matrix for Peer Review</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>evidence_type_counts.csv</t>
+          <t>gbls_feature_overview.xlsx</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Excel workbook with dashboard and per-field sheets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Counts for Evidence Type</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>evidence_type_matrix.csv</t>
+          <t>generated_artifact_manifest.json</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Manifest of all generated files with sizes and timestamp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Binary matrix for Evidence Type</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>primary_methodology_counts.csv</t>
+          <t>source_type_matrix.csv</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Binary article × Source_Type matrix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Counts for Primary Methodology</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>article_id</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>primary_methodology_matrix.csv</t>
+          <t>source_type_counts.csv</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Aggregate counts for Source_Type</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Binary matrix for Primary Methodology</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>feature_group + feature_value</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>library_context_counts.csv</t>
+          <t>peer_review_matrix.csv</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Binary article × Peer_Review matrix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Counts for Library Context</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>article_id</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>library_context_matrix.csv</t>
+          <t>peer_review_counts.csv</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Aggregate counts for Peer_Review</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Binary matrix for Library Context</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>feature_group + feature_value</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>game_format_counts.csv</t>
+          <t>evidence_type_matrix.csv</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Binary article × Evidence_Type matrix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Counts for Game Format</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>article_id</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>game_format_matrix.csv</t>
+          <t>evidence_type_counts.csv</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Aggregate counts for Evidence_Type</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Binary matrix for Game Format</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>feature_group + feature_value</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>service_area_counts.csv</t>
+          <t>primary_methodology_matrix.csv</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Binary article × Primary_Methodology matrix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Counts for Service Area</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>article_id</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>service_area_matrix.csv</t>
+          <t>primary_methodology_counts.csv</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Aggregate counts for Primary_Methodology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Binary matrix for Service Area</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>feature_group + feature_value</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>audience_counts.csv</t>
+          <t>library_context_matrix.csv</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Binary article × Library_Context matrix</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Counts for Audience</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>article_id</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>audience_matrix.csv</t>
+          <t>library_context_counts.csv</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Aggregate counts for Library_Context</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Binary matrix for Audience</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>feature_group + feature_value</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>intended_outcome_counts.csv</t>
+          <t>game_format_matrix.csv</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Binary article × Game_Format matrix</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Counts for Intended Outcome</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>article_id</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>intended_outcome_matrix.csv</t>
+          <t>game_format_counts.csv</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>one row per article</t>
+          <t>Aggregate counts for Game_Format</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Binary matrix for Intended Outcome</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>article_id</t>
+          <t>feature_group + feature_value</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>coding_confidence_counts.csv</t>
+          <t>service_area_matrix.csv</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>one row per feature label</t>
+          <t>Binary article × Service_Area matrix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Counts for Coding Confidence</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>feature_value</t>
+          <t>article_id</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>service_area_counts.csv</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aggregate counts for Service_Area</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>feature_group + feature_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>audience_matrix.csv</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Binary article × Audience matrix</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>article_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>audience_counts.csv</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aggregate counts for Audience</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>feature_group + feature_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>intended_outcome_matrix.csv</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Binary article × Intended_Outcome matrix</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>article_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>intended_outcome_counts.csv</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Aggregate counts for Intended_Outcome</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>feature_group + feature_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>coding_confidence_matrix.csv</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>one row per article</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Binary matrix for Coding Confidence</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Binary article × Coding_Confidence matrix</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>article_id</t>
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>coding_confidence_counts.csv</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Aggregate counts for Coding_Confidence</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>feature_group + feature_value</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D31"/>
+  <autoFilter ref="A1:C37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5098,44 +4948,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -5144,269 +4988,214 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>peer_reviewed_journal_article</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>116</v>
+      </c>
       <c r="C2" t="n">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>toolkit_or_guidance_document</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>31</v>
+      </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>15.5</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>professional_publication</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>22</v>
+      </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>conference_paper</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>4.5</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>book_chapter</t>
-        </is>
+          <t>dataset_or_archive</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>dataset_or_archive</t>
-        </is>
+          <t>book_chapter</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>blog_or_web_article</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>book</t>
-        </is>
+          <t>dissertation_or_thesis</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dissertation_or_thesis</t>
-        </is>
+          <t>government_or_foundation_report</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>government_or_foundation_report</t>
-        </is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>unpublished_document</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F12" t="n">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5417,44 +5206,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -5463,101 +5246,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>peer_review</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>peer_reviewed</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>116</v>
+      </c>
       <c r="C2" t="n">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>peer_review</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>editorial_reviewed</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>39</v>
+      </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>19.5</v>
       </c>
       <c r="E3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>peer_review</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>unknown</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>35</v>
+      </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>17.5</v>
       </c>
       <c r="E4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>peer_review</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>not_applicable</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5568,44 +5331,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -5614,173 +5371,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>empirical_study</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>79</v>
+      </c>
       <c r="C2" t="n">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>39.5</v>
       </c>
       <c r="E2" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>practitioner_reflection</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>58</v>
+      </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>theoretical_or_conceptual</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>26</v>
+      </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>implementation_case</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>24</v>
+      </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>evidence_synthesis</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>13</v>
+      </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>6.5</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>instrument_or_framework_development</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>13</v>
+      </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>6.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>content_or_artifact_analysis</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5791,44 +5513,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -5837,293 +5553,233 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>none</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>51</v>
+      </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>25.5</v>
       </c>
       <c r="E2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>theoretical_or_conceptual</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>28</v>
+      </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>case_or_design_study</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>24</v>
+      </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>mixed_methods</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>21</v>
+      </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>10.5</v>
       </c>
       <c r="E5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
           <t>qualitative_study</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>experimental_study</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>survey</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>evidence_synthesis</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>6.5</v>
       </c>
       <c r="E9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F9" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>content_analysis</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
           <t>historical_analysis</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>participatory_design</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>primary_methodology</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
           <t>action_research</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D13" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" t="n">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:E13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6134,44 +5790,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>feature_group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>feature_value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>article_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>total_articles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>article_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>rank_within_group</t>
         </is>
@@ -6180,197 +5830,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>non_library_context</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>47</v>
+      </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>23.5</v>
       </c>
       <c r="E2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>unspecified_library_context</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>47</v>
+      </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>23.5</v>
       </c>
       <c r="E3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
           <t>public_library</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>30</v>
+      </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>academic_library</t>
-        </is>
+          <t>cultural_heritage_institution</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>cultural_heritage_institution</t>
-        </is>
+          <t>academic_library</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
           <t>multiple_library_types</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>20</v>
+      </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>school_library</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>4.5</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>library_context</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
           <t>library_school</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F9" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2_calculated_metrics/gbls_corpus_metrics/gbls_feature_overview.xlsx
+++ b/2_calculated_metrics/gbls_corpus_metrics/gbls_feature_overview.xlsx
@@ -12,36 +12,32 @@
     <sheet name="All Feature Counts" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Data Dictionary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Source_Type" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Peer_Review" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Evidence_Type" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Primary_Methodology" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Evidence_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Primary_Methodology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Conceptual_Theme" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Library_Context" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Game_Format" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Service_Area" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Audience" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Service_Audience" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Intended_Outcome" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Evidence_Confidence" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Service_Conditions_Addressed" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Conceptual_Theme" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Coding_Confidence" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Year Counts'!$A$1:$C$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Feature Counts'!$A$1:$F$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Dictionary'!$A$1:$C$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Source_Type'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Peer_Review'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Evidence_Type'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Primary_Methodology'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Year Counts'!$A$1:$C$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Feature Counts'!$A$1:$F$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data Dictionary'!$A$1:$C$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Source_Type'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Evidence_Type'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Primary_Methodology'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Conceptual_Theme'!$A$1:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Library_Context'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Game_Format'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Service_Area'!$A$1:$E$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Audience'!$A$1:$E$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Intended_Outcome'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Evidence_Confidence'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Service_Conditions_Addressed'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Conceptual_Theme'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Coding_Confidence'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Game_Format'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Service_Area'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Service_Audience'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Intended_Outcome'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Evidence_Confidence'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Service_Conditions_Addressed'!$A$1:$E$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -497,7 +493,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +513,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +523,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
@@ -537,7 +533,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2377</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +543,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.612</v>
+        <v>16.035</v>
       </c>
     </row>
     <row r="10">
@@ -557,7 +553,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>604</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11">
@@ -567,7 +563,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
@@ -577,7 +573,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13"/>
@@ -605,49 +601,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Peer_Review</t>
+          <t>Evidence_Type</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Evidence_Type</t>
+          <t>Primary_Methodology</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Primary_Methodology</t>
+          <t>Conceptual_Theme</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>208</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19">
@@ -660,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
@@ -670,10 +666,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>208</v>
+        <v>399</v>
       </c>
     </row>
     <row r="21">
@@ -683,23 +679,23 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>359</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Audience</t>
+          <t>Service_Audience</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>245</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23">
@@ -709,10 +705,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>272</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25">
@@ -735,36 +731,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Conceptual_Theme</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Coding_Confidence</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" t="n">
-        <v>208</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -778,7 +748,1430 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>feature_value</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>article_count</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_articles</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>article_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>rank_within_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>digital_game</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>114</v>
+      </c>
+      <c r="C2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tabletop_game</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tabletop_roleplaying_game</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>virtual_or_augmented_reality</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>game_creation</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" t="n">
+        <v>227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gamification</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C7" t="n">
+        <v>227</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>escape_room_or_breakout_box</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" t="n">
+        <v>227</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>unspecified_game_format</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="n">
+        <v>227</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>toy_or_open_play</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>227</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>megagame</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>227</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>card_game</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>227</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mobile_game</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>227</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>live_action_roleplaying_game</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>227</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pervasive_game</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>227</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>board_game</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>227</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>227</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>console_game</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>227</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>pc_game</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>227</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>augmented_reality</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>227</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3D_virtual_world</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>227</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>227</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>227</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>console</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>227</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>feature_value</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>article_count</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_articles</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>article_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>rank_within_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>learning_and_literacy</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>163</v>
+      </c>
+      <c r="C2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>community_and_inclusion</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>76</v>
+      </c>
+      <c r="C3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>collections_and_access</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>65</v>
+      </c>
+      <c r="C4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>programming_and_facilitation</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>discovery_and_advisory</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n">
+        <v>227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>outreach_and_partnerships</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>38</v>
+      </c>
+      <c r="C7" t="n">
+        <v>227</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cultural_heritage_and_research</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>227</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>creation_and_making</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" t="n">
+        <v>227</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>professional_capacity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="n">
+        <v>227</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>227</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>wellness_and_resilience</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>227</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>space_and_infrastructure</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>227</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>feature_value</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>article_count</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_articles</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>article_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>rank_within_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>general_public</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>students</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>86</v>
+      </c>
+      <c r="C3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>teens</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>children</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adults</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>227</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>educators</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>227</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>underserved_or_special_population</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>227</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>young_adults</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>227</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>families</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>227</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>feature_value</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>article_count</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_articles</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>article_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>rank_within_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>learning_and_literacy</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>102</v>
+      </c>
+      <c r="C2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>engagement_and_participation</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>equitable_access</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>discovery_and_advisory</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
+        <v>227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cultural_stewardship_and_preservation</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>227</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>227</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>belonging_and_community</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>227</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>institutional_capacity</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>227</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>wellness_and_resilience</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>227</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>creativity_and_production</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>227</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>feature_value</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>article_count</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>total_articles</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>article_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>rank_within_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>demonstrated_outcome</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>89</v>
+      </c>
+      <c r="C2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>practitioner_knowledge</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>54</v>
+      </c>
+      <c r="C3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>descriptive_only</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n">
+        <v>227</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>theoretical_or_conceptual</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>34</v>
+      </c>
+      <c r="C5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>promising_evidence</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>evidence_synthesis</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>227</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -818,17 +2211,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>digital_game</t>
+          <t>skilled_facilitation_required</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D2" t="n">
-        <v>28.1</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -837,17 +2230,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>multiple_game_formats</t>
+          <t>access_infrastructure_required</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>22.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -856,17 +2249,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tabletop_game</t>
+          <t>inclusive_design_or_accessibility</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="C4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>8.9</v>
+        <v>55.1</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -875,17 +2268,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tabletop_roleplaying_game</t>
+          <t>evaluation_or_reflection</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D5" t="n">
-        <v>8.5</v>
+        <v>32.6</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -894,17 +2287,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gamification</t>
+          <t>community_assessment_needed</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D6" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -913,109 +2306,109 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>virtual_or_augmented_reality</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D7" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unspecified_game_format</t>
+          <t>sustainable_operations</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D8" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>escape_room_or_breakout_box</t>
+          <t>none</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>227</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E9" t="n">
         <v>8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>toy_or_open_play</t>
+          <t>institutional_capacity</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>game_creation</t>
+          <t>select, describe, and provide access to appropriate games</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[tabletop_game, digital_game, escape_room_or_breakout_box, gamification]</t>
+          <t>facilitate inclusive and meaningful participation</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D12" t="n">
         <v>0.4</v>
@@ -1024,1434 +2417,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pervasive_game</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>224</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>feature_value</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>article_count</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_articles</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>article_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>rank_within_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>learning_and_literacy</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>collections_and_access</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>77</v>
-      </c>
-      <c r="C3" t="n">
-        <v>224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>programming_and_facilitation</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>56</v>
-      </c>
-      <c r="C4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>discovery_and_advisory</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>35</v>
-      </c>
-      <c r="C5" t="n">
-        <v>224</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>community_and_inclusion</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>29</v>
-      </c>
-      <c r="C6" t="n">
-        <v>224</v>
-      </c>
-      <c r="D6" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>professional_capacity</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>19</v>
-      </c>
-      <c r="C7" t="n">
-        <v>224</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cultural_heritage_and_research</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C8" t="n">
-        <v>224</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>space_and_infrastructure</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>13</v>
-      </c>
-      <c r="C9" t="n">
-        <v>224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>outreach_and_partnerships</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>224</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>creation_and_making</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>224</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>224</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>space_and_infrastructure, professional_capacity</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>224</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>learning_and_literacy, community_and_inclusion</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>224</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>space_and_infrastructure, community_and_inclusion</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>224</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>[collections_and_access, programming_and_facilitation, learning_and_literacy, outreach_and_partnerships, professional_capacity]</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>224</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>engagement_and_participation, programming_and_facilitation</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>224</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E17"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>feature_value</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>article_count</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_articles</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>article_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>rank_within_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>125</v>
-      </c>
-      <c r="C2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>students</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>teens</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>children</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C5" t="n">
-        <v>224</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>general_public</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>224</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>families</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>224</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>educators</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>224</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>underserved_or_special_population</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>young_adults</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" t="n">
-        <v>224</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>educators, teens</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>224</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>older_adults</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>224</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>[students, educators]</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>224</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adults</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>224</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E14"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>feature_value</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>article_count</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_articles</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>article_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>rank_within_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>95</v>
-      </c>
-      <c r="C2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>learning_and_literacy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>64</v>
-      </c>
-      <c r="C3" t="n">
-        <v>224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>discovery_and_advisory</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D4" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>belonging_and_community</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C5" t="n">
-        <v>224</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>creativity_and_production</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C6" t="n">
-        <v>224</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>institutional_capacity</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C7" t="n">
-        <v>224</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>equitable_access</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C8" t="n">
-        <v>224</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>engagement_and_participation</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" t="n">
-        <v>224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cultural_stewardship_and_preservation</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" t="n">
-        <v>224</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>wellness_and_resilience</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>224</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>learning_and_literacy, belonging_and_community</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>224</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>[equitable_access, learning_and_literacy, engagement_and_participation, institutional_capacity]</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>224</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E13"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>feature_value</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>article_count</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_articles</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>article_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>rank_within_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>theoretical_or_conceptual</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>practitioner_knowledge</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>feature_value</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>article_count</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_articles</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>article_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>rank_within_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>community_assessment_needed, skilled_facilitation_required</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>[access_infrastructure_required, skilled_facilitation_required, inclusive_design_or_accessibility, evaluation_or_reflection]</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>feature_value</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>article_count</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_articles</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>article_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>rank_within_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>not_identified</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>service_ecology</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>information_behavior_and_practice, service_ecology</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>information_behavior_and_practice, educational_psychology, games_as_cultural_media</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>224</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>service_ecology, information_behavior_and_practice</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>224</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>[service_ecology, conditional_benefits]</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>224</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>feature_value</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>article_count</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>total_articles</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>article_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>rank_within_group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>201</v>
-      </c>
-      <c r="C2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D2" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>224</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2462,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2516,20 +2483,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2542,27 +2509,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -2611,10 +2578,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="12">
@@ -2627,7 +2594,7 @@
         <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -2637,10 +2604,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -2653,7 +2620,7 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -2663,10 +2630,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16">
@@ -2676,10 +2643,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="17">
@@ -2689,10 +2656,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18">
@@ -2702,10 +2669,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2718,7 +2685,7 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="20">
@@ -2728,10 +2695,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="21">
@@ -2741,10 +2708,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>12.9</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="22">
@@ -2757,7 +2724,7 @@
         <v>41</v>
       </c>
       <c r="C22" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="23">
@@ -2767,27 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" t="n">
-        <v>7.6</v>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C24"/>
+  <autoFilter ref="A1:C25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2798,7 +2778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2844,22 +2824,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>games_as_cultural_media</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E2" t="n">
-        <v>55.8</v>
+        <v>59.9</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -2868,22 +2848,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>students</t>
+          <t>information_behavior_and_practice</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="D3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E3" t="n">
-        <v>22.8</v>
+        <v>50.2</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -2892,22 +2872,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>teens</t>
+          <t>service_ecology</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>33.9</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -2916,22 +2896,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>children</t>
+          <t>game_literacy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D5" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8</v>
+        <v>29.1</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -2940,22 +2920,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>general_public</t>
+          <t>educational_psychology</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>26.9</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -2964,22 +2944,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>families</t>
+          <t>participatory_culture_and_production</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>18.9</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
@@ -2988,46 +2968,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>educators</t>
+          <t>social_equity_and_access</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>43</v>
+      </c>
+      <c r="D8" t="n">
+        <v>227</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F8" t="n">
         <v>6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>224</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>underserved_or_special_population</t>
+          <t>multiple_themes</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
@@ -3036,142 +3016,142 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>young_adults</t>
+          <t>conditional_benefits</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>educators, teens</t>
+          <t>games_as_participatory_culture_and_production</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>older_adults</t>
+          <t>community_and_inclusion</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[students, educators]</t>
+          <t>games_as_participatory_and_expressive_media</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>conceptual_theme</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>adults</t>
+          <t>not_identified</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E14" t="n">
         <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
+          <t>evidence_confidence</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>demonstrated_outcome</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>201</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E15" t="n">
-        <v>89.7</v>
+        <v>39.2</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -3180,22 +3160,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
+          <t>evidence_confidence</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>practitioner_knowledge</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>23.8</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -3204,22 +3184,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>coding_confidence</t>
+          <t>evidence_confidence</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>descriptive_only</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
         <v>3</v>
@@ -3228,118 +3208,118 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>conceptual_theme</t>
+          <t>evidence_confidence</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_identified</t>
+          <t>theoretical_or_conceptual</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" t="n">
+        <v>227</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>224</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>conceptual_theme</t>
+          <t>evidence_confidence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>service_ecology</t>
+          <t>promising_evidence</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>conceptual_theme</t>
+          <t>evidence_confidence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>information_behavior_and_practice, service_ecology</t>
+          <t>evidence_synthesis</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>conceptual_theme</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>information_behavior_and_practice, educational_psychology, games_as_cultural_media</t>
+          <t>empirical_study</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>227</v>
+      </c>
+      <c r="E21" t="n">
+        <v>33</v>
+      </c>
+      <c r="F21" t="n">
         <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>224</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>conceptual_theme</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>service_ecology, information_behavior_and_practice</t>
+          <t>practitioner_reflection</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4</v>
+        <v>28.6</v>
       </c>
       <c r="F22" t="n">
         <v>2</v>
@@ -3348,31 +3328,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>conceptual_theme</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[service_ecology, conditional_benefits]</t>
+          <t>evidence_synthesis</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D23" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>14.1</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>evidence_confidence</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3381,64 +3361,64 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>28</v>
+      </c>
+      <c r="D24" t="n">
+        <v>227</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F24" t="n">
         <v>4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>224</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>evidence_confidence</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>practitioner_knowledge</t>
+          <t>implementation_case</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>evidence_confidence</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>content_or_artifact_analysis</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -3449,20 +3429,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>empirical_study</t>
+          <t>historical_analysis</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E27" t="n">
-        <v>33.9</v>
+        <v>0.4</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -3473,164 +3453,164 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>practitioner_reflection</t>
+          <t>content_analysis</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E28" t="n">
-        <v>17.4</v>
+        <v>0.4</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>theoretical_or_conceptual</t>
+          <t>digital_game</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D29" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E29" t="n">
-        <v>11.6</v>
+        <v>50.2</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>implementation_case</t>
+          <t>tabletop_game</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D30" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E30" t="n">
-        <v>10.7</v>
+        <v>36.6</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>professional_practice_artifact</t>
+          <t>tabletop_roleplaying_game</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D31" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E31" t="n">
-        <v>8.9</v>
+        <v>24.2</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>evidence_synthesis</t>
+          <t>virtual_or_augmented_reality</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E32" t="n">
-        <v>7.6</v>
+        <v>14.1</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>instrument_or_framework_development</t>
+          <t>game_creation</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D33" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E33" t="n">
-        <v>6.7</v>
+        <v>12.8</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>evidence_type</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>content_or_artifact_analysis</t>
+          <t>gamification</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E34" t="n">
-        <v>5.4</v>
+        <v>10.1</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -3641,20 +3621,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>digital_game</t>
+          <t>escape_room_or_breakout_box</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D35" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E35" t="n">
-        <v>28.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -3665,20 +3645,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>multiple_game_formats</t>
+          <t>unspecified_game_format</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E36" t="n">
-        <v>22.3</v>
+        <v>5.7</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -3689,20 +3669,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>tabletop_game</t>
+          <t>toy_or_open_play</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E37" t="n">
-        <v>8.9</v>
+        <v>3.5</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -3713,20 +3693,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tabletop_roleplaying_game</t>
+          <t>megagame</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E38" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -3737,20 +3717,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gamification</t>
+          <t>card_game</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E39" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -3761,20 +3741,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>virtual_or_augmented_reality</t>
+          <t>mobile_game</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E40" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -3785,20 +3765,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>unspecified_game_format</t>
+          <t>live_action_roleplaying_game</t>
         </is>
       </c>
       <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>227</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F41" t="n">
         <v>12</v>
-      </c>
-      <c r="D41" t="n">
-        <v>224</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F41" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -3809,20 +3789,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>escape_room_or_breakout_box</t>
+          <t>pervasive_game</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E42" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -3833,20 +3813,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>toy_or_open_play</t>
+          <t>board_game</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E43" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -3857,20 +3837,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>game_creation</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E44" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
@@ -3881,20 +3861,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[tabletop_game, digital_game, escape_room_or_breakout_box, gamification]</t>
+          <t>console_game</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E45" t="n">
         <v>0.4</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -3905,140 +3885,140 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pervasive_game</t>
+          <t>pc_game</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E46" t="n">
         <v>0.4</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>augmented_reality</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E47" t="n">
-        <v>42.4</v>
+        <v>0.4</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>learning_and_literacy</t>
+          <t>3D_virtual_world</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E48" t="n">
-        <v>28.6</v>
+        <v>0.4</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>discovery_and_advisory</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E49" t="n">
-        <v>11.2</v>
+        <v>0.4</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>belonging_and_community</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E50" t="n">
-        <v>8.9</v>
+        <v>0.4</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>intended_outcome</t>
+          <t>game_format</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>creativity_and_production</t>
+          <t>console</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E51" t="n">
-        <v>7.6</v>
+        <v>0.4</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -4049,20 +4029,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>institutional_capacity</t>
+          <t>learning_and_literacy</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D52" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E52" t="n">
-        <v>6.2</v>
+        <v>44.9</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4073,20 +4053,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>equitable_access</t>
+          <t>engagement_and_participation</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D53" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E53" t="n">
-        <v>6.2</v>
+        <v>23.3</v>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -4097,20 +4077,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>engagement_and_participation</t>
+          <t>equitable_access</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D54" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E54" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -4121,20 +4101,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cultural_stewardship_and_preservation</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D55" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E55" t="n">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -4145,20 +4125,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>wellness_and_resilience</t>
+          <t>discovery_and_advisory</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E56" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="F56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -4169,20 +4149,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>learning_and_literacy, belonging_and_community</t>
+          <t>cultural_stewardship_and_preservation</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -4193,116 +4173,116 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[equitable_access, learning_and_literacy, engagement_and_participation, institutional_capacity]</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>non_library_context</t>
+          <t>belonging_and_community</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E59" t="n">
-        <v>21.9</v>
+        <v>2.2</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>unspecified_library_context</t>
+          <t>institutional_capacity</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E60" t="n">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>public_library</t>
+          <t>wellness_and_resilience</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E61" t="n">
-        <v>13.8</v>
+        <v>1.8</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>library_context</t>
+          <t>intended_outcome</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>academic_library</t>
+          <t>creativity_and_production</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E62" t="n">
-        <v>11.2</v>
+        <v>1.3</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -4313,20 +4293,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>multiple_library_types</t>
+          <t>academic_library</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D63" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E63" t="n">
-        <v>9.800000000000001</v>
+        <v>29.5</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4337,20 +4317,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cultural_heritage_institution</t>
+          <t>non_library_context</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D64" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E64" t="n">
-        <v>9.800000000000001</v>
+        <v>29.1</v>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4361,20 +4341,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>school_library</t>
+          <t>public_library</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="D65" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>23.8</v>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4385,116 +4365,116 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>library_school</t>
+          <t>school_library</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D66" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E66" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>peer_reviewed</t>
+          <t>multiple_library_types</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="D67" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E67" t="n">
-        <v>53.1</v>
+        <v>4.8</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>editorial_reviewed</t>
+          <t>cultural_heritage_institution</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E68" t="n">
-        <v>19.6</v>
+        <v>3.1</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>library_school</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E69" t="n">
-        <v>15.6</v>
+        <v>2.6</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>peer_review</t>
+          <t>library_context</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>unspecified_library_context</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E70" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -4509,13 +4489,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D71" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E71" t="n">
-        <v>16.5</v>
+        <v>21.1</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -4529,17 +4509,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>theoretical_or_conceptual</t>
+          <t>evidence_synthesis</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D72" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E72" t="n">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -4553,20 +4533,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>case_or_design_study</t>
+          <t>qualitative_study</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D73" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E73" t="n">
-        <v>10.3</v>
+        <v>13.7</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4577,20 +4557,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>mixed_methods</t>
+          <t>case_or_design_study</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D74" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E74" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="F74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4601,20 +4581,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>community_curation</t>
+          <t>mixed_methods</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D75" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E75" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -4625,20 +4605,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>qualitative_study</t>
+          <t>content_analysis</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D76" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E76" t="n">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -4649,20 +4629,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>evidence_synthesis</t>
+          <t>theoretical_or_conceptual</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D77" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E77" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="F77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -4673,14 +4653,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>experimental_study</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E78" t="n">
         <v>6.2</v>
@@ -4697,20 +4677,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>experimental_study</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E79" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="F79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -4721,20 +4701,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>content_analysis</t>
+          <t>historical_analysis</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E80" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="F80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
@@ -4745,20 +4725,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>historical_analysis</t>
+          <t>action_research</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E81" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="F81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -4769,17 +4749,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>participatory_design</t>
+          <t>practitioner_reflection</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E82" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F82" t="n">
         <v>10</v>
@@ -4793,14 +4773,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>action_research</t>
+          <t>quasi-experimental</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E83" t="n">
         <v>0.4</v>
@@ -4812,49 +4792,49 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>learning_and_literacy</t>
+          <t>empirical_study</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E84" t="n">
-        <v>44.2</v>
+        <v>0.4</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>primary_methodology</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>collections_and_access</t>
+          <t>cognitive_ethnography</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E85" t="n">
-        <v>34.4</v>
+        <v>0.4</v>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
@@ -4865,20 +4845,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>programming_and_facilitation</t>
+          <t>learning_and_literacy</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="D86" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E86" t="n">
-        <v>25</v>
+        <v>71.8</v>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4889,20 +4869,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>discovery_and_advisory</t>
+          <t>community_and_inclusion</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D87" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E87" t="n">
-        <v>15.6</v>
+        <v>33.5</v>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4913,20 +4893,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>community_and_inclusion</t>
+          <t>collections_and_access</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="D88" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E88" t="n">
-        <v>12.9</v>
+        <v>28.6</v>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -4937,20 +4917,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>professional_capacity</t>
+          <t>programming_and_facilitation</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D89" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E89" t="n">
-        <v>8.5</v>
+        <v>22.5</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -4961,20 +4941,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>cultural_heritage_and_research</t>
+          <t>discovery_and_advisory</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D90" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E90" t="n">
-        <v>6.7</v>
+        <v>18.5</v>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -4985,20 +4965,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>space_and_infrastructure</t>
+          <t>outreach_and_partnerships</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D91" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E91" t="n">
-        <v>5.8</v>
+        <v>16.7</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -5009,20 +4989,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>outreach_and_partnerships</t>
+          <t>cultural_heritage_and_research</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D92" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E92" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -5037,16 +5017,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D93" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E93" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94">
@@ -5057,20 +5037,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>professional_capacity</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D94" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="F94" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -5081,20 +5061,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>space_and_infrastructure, professional_capacity</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E95" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="F95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -5105,20 +5085,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>learning_and_literacy, community_and_inclusion</t>
+          <t>wellness_and_resilience</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -5129,14 +5109,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>space_and_infrastructure, community_and_inclusion</t>
+          <t>space_and_infrastructure</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E97" t="n">
         <v>0.4</v>
@@ -5148,55 +5128,55 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[collections_and_access, programming_and_facilitation, learning_and_literacy, outreach_and_partnerships, professional_capacity]</t>
+          <t>general_public</t>
         </is>
       </c>
       <c r="C98" t="n">
+        <v>100</v>
+      </c>
+      <c r="D98" t="n">
+        <v>227</v>
+      </c>
+      <c r="E98" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F98" t="n">
         <v>1</v>
-      </c>
-      <c r="D98" t="n">
-        <v>224</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F98" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>engagement_and_participation, programming_and_facilitation</t>
+          <t>students</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="D99" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E99" t="n">
-        <v>0.4</v>
+        <v>37.9</v>
       </c>
       <c r="F99" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>service_conditions_addressed</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5205,356 +5185,692 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D100" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E100" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>service_conditions_addressed</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>community_assessment_needed, skilled_facilitation_required</t>
+          <t>teens</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>service_conditions_addressed</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[access_infrastructure_required, skilled_facilitation_required, inclusive_design_or_accessibility, evaluation_or_reflection]</t>
+          <t>children</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E102" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>peer_reviewed_journal_article</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E103" t="n">
-        <v>52.7</v>
+        <v>1.8</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>professional_publication</t>
+          <t>educators</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E104" t="n">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>professional_community_working_document</t>
+          <t>underserved_or_special_population</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E105" t="n">
-        <v>8.9</v>
+        <v>1.3</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>toolkit_or_guidance_document</t>
+          <t>young_adults</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E106" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="F106" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_audience</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>conference_paper</t>
+          <t>families</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E107" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="F107" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_conditions_addressed</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>skilled_facilitation_required</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>179</v>
       </c>
       <c r="D108" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E108" t="n">
-        <v>2.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_conditions_addressed</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>dataset_or_archive</t>
+          <t>access_infrastructure_required</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="D109" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E109" t="n">
-        <v>2.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_conditions_addressed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>book_chapter</t>
+          <t>inclusive_design_or_accessibility</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="D110" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E110" t="n">
-        <v>2.7</v>
+        <v>55.1</v>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_conditions_addressed</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>government_or_foundation_report</t>
+          <t>evaluation_or_reflection</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="D111" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E111" t="n">
-        <v>1.3</v>
+        <v>32.6</v>
       </c>
       <c r="F111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_conditions_addressed</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>blog_or_web_article</t>
+          <t>community_assessment_needed</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D112" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E112" t="n">
-        <v>1.3</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>service_conditions_addressed</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>dissertation_or_thesis</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D113" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>service_conditions_addressed</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>sustainable_operations</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>6</v>
+      </c>
+      <c r="D114" t="n">
+        <v>227</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F114" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>service_conditions_addressed</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>227</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>service_conditions_addressed</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>institutional_capacity</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>227</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F116" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>service_conditions_addressed</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>select, describe, and provide access to appropriate games</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>227</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F117" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>service_conditions_addressed</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>facilitate inclusive and meaningful participation</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>227</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F118" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>source_type</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>peer_reviewed_journal_article</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>154</v>
+      </c>
+      <c r="D119" t="n">
+        <v>227</v>
+      </c>
+      <c r="E119" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>professional_publication</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>43</v>
+      </c>
+      <c r="D120" t="n">
+        <v>227</v>
+      </c>
+      <c r="E120" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>blog_or_web_article</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>9</v>
+      </c>
+      <c r="D121" t="n">
+        <v>227</v>
+      </c>
+      <c r="E121" t="n">
+        <v>4</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>6</v>
+      </c>
+      <c r="D122" t="n">
+        <v>227</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>conference_paper</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>6</v>
+      </c>
+      <c r="D123" t="n">
+        <v>227</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F123" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>book_chapter</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" t="n">
+        <v>227</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F124" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>dissertation_or_thesis</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>227</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>conference_presentation</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>227</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
         <is>
           <t>unpublished_document</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="C127" t="n">
         <v>1</v>
       </c>
-      <c r="D114" t="n">
-        <v>224</v>
-      </c>
-      <c r="E114" t="n">
+      <c r="D127" t="n">
+        <v>227</v>
+      </c>
+      <c r="E127" t="n">
         <v>0.4</v>
       </c>
-      <c r="F114" t="n">
-        <v>9</v>
+      <c r="F127" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>government_or_foundation_report</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>227</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F128" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F114"/>
+  <autoFilter ref="A1:F128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5565,7 +5881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -5899,12 +6215,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>peer_review_matrix.csv</t>
+          <t>evidence_type_matrix.csv</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Binary article × Peer_Review matrix</t>
+          <t>Binary article × Evidence_Type matrix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5916,12 +6232,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>peer_review_counts.csv</t>
+          <t>evidence_type_counts.csv</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aggregate counts for Peer_Review</t>
+          <t>Aggregate counts for Evidence_Type</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5933,12 +6249,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>evidence_type_matrix.csv</t>
+          <t>primary_methodology_matrix.csv</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Binary article × Evidence_Type matrix</t>
+          <t>Binary article × Primary_Methodology matrix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5950,12 +6266,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>evidence_type_counts.csv</t>
+          <t>primary_methodology_counts.csv</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aggregate counts for Evidence_Type</t>
+          <t>Aggregate counts for Primary_Methodology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5967,12 +6283,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>primary_methodology_matrix.csv</t>
+          <t>conceptual_theme_matrix.csv</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Binary article × Primary_Methodology matrix</t>
+          <t>Binary article × Conceptual_Theme matrix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5984,12 +6300,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>primary_methodology_counts.csv</t>
+          <t>conceptual_theme_counts.csv</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aggregate counts for Primary_Methodology</t>
+          <t>Aggregate counts for Conceptual_Theme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6103,12 +6419,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>audience_matrix.csv</t>
+          <t>service_audience_matrix.csv</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Binary article × Audience matrix</t>
+          <t>Binary article × Service_Audience matrix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6120,12 +6436,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>audience_counts.csv</t>
+          <t>service_audience_counts.csv</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aggregate counts for Audience</t>
+          <t>Aggregate counts for Service_Audience</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6236,76 +6552,8 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>conceptual_theme_matrix.csv</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Binary article × Conceptual_Theme matrix</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>article_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>conceptual_theme_counts.csv</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Aggregate counts for Conceptual_Theme</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>feature_group + feature_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>coding_confidence_matrix.csv</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Binary article × Coding_Confidence matrix</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>article_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>coding_confidence_counts.csv</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Aggregate counts for Coding_Confidence</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>feature_group + feature_value</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C43"/>
+  <autoFilter ref="A1:C39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6316,10 +6564,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -6360,13 +6608,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D2" t="n">
-        <v>52.7</v>
+        <v>67.8</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6379,13 +6627,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>9.800000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -6394,17 +6642,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>professional_community_working_document</t>
+          <t>blog_or_web_article</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>8.9</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -6413,17 +6661,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>toolkit_or_guidance_document</t>
+          <t>book</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -6436,51 +6684,51 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>book_chapter</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dataset_or_archive</t>
+          <t>dissertation_or_thesis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
@@ -6489,17 +6737,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>book_chapter</t>
+          <t>conference_presentation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -6508,17 +6756,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>government_or_foundation_report</t>
+          <t>unpublished_document</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
@@ -6527,62 +6775,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>blog_or_web_article</t>
+          <t>government_or_foundation_report</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dissertation_or_thesis</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>224</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>unpublished_document</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>224</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6593,10 +6803,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -6633,17 +6843,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>peer_reviewed</t>
+          <t>empirical_study</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D2" t="n">
-        <v>53.1</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6652,17 +6862,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>editorial_reviewed</t>
+          <t>practitioner_reflection</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>19.6</v>
+        <v>28.6</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -6671,17 +6881,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>evidence_synthesis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.1</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -6690,24 +6900,100 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>theoretical_or_conceptual</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5</v>
+        <v>12.3</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>implementation_case</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>content_or_artifact_analysis</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>227</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>historical_analysis</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>227</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>content_analysis</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>227</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6718,10 +7004,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -6758,17 +7044,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>empirical_study</t>
+          <t>none</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D2" t="n">
-        <v>33.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6777,17 +7063,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>practitioner_reflection</t>
+          <t>evidence_synthesis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>13.7</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -6796,119 +7082,252 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>theoretical_or_conceptual</t>
+          <t>qualitative_study</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>implementation_case</t>
+          <t>case_or_design_study</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D5" t="n">
-        <v>10.7</v>
+        <v>12.8</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>professional_practice_artifact</t>
+          <t>mixed_methods</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D6" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>evidence_synthesis</t>
+          <t>content_analysis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D7" t="n">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>instrument_or_framework_development</t>
+          <t>theoretical_or_conceptual</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D8" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>content_or_artifact_analysis</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="E9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>experimental_study</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>227</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E10" t="n">
         <v>8</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>historical_analysis</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>227</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>action_research</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>227</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>practitioner_reflection</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>227</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quasi-experimental</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>227</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>empirical_study</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>227</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cognitive_ethnography</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>227</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6922,7 +7341,7 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -6959,17 +7378,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>games_as_cultural_media</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5</v>
+        <v>59.9</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6978,17 +7397,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>theoretical_or_conceptual</t>
+          <t>information_behavior_and_practice</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>14.3</v>
+        <v>50.2</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -6997,17 +7416,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>case_or_design_study</t>
+          <t>service_ecology</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>10.3</v>
+        <v>33.9</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -7016,17 +7435,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mixed_methods</t>
+          <t>game_literacy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D5" t="n">
-        <v>9.4</v>
+        <v>29.1</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -7035,17 +7454,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>community_curation</t>
+          <t>educational_psychology</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D6" t="n">
-        <v>8.9</v>
+        <v>26.9</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -7054,17 +7473,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>qualitative_study</t>
+          <t>participatory_culture_and_production</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D7" t="n">
-        <v>7.6</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -7073,36 +7492,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>evidence_synthesis</t>
+          <t>social_equity_and_access</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D8" t="n">
-        <v>6.2</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>experimental_study</t>
+          <t>multiple_themes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -7111,55 +7530,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>conditional_benefits</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>content_analysis</t>
+          <t>games_as_participatory_culture_and_production</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>historical_analysis</t>
+          <t>community_and_inclusion</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="E12" t="n">
         <v>9</v>
@@ -7168,39 +7587,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>participatory_design</t>
+          <t>games_as_participatory_and_expressive_media</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>action_research</t>
+          <t>not_identified</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D14" t="n">
         <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7255,17 +7674,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>non_library_context</t>
+          <t>academic_library</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D2" t="n">
-        <v>21.9</v>
+        <v>29.5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -7274,17 +7693,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>unspecified_library_context</t>
+          <t>non_library_context</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>29.1</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -7297,13 +7716,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D4" t="n">
-        <v>13.8</v>
+        <v>23.8</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -7312,17 +7731,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>academic_library</t>
+          <t>school_library</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D5" t="n">
-        <v>11.2</v>
+        <v>6.6</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -7335,13 +7754,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D6" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -7354,54 +7773,54 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D7" t="n">
-        <v>9.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>school_library</t>
+          <t>library_school</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>library_school</t>
+          <t>unspecified_library_context</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
